--- a/04_DESIGN_TABLES/DesignTable_2700.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2700.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2233,24 +2238,50 @@
           <t>2700-02-02</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.062</v>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>2700-02-02</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5/16-24 x 5/16-24 (JIC) + bulkhead</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L4@DRIVE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "L LGTH" = "1.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; C2HEX@HEX: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 12/13 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2700-06-04 0.69 vs 0.812); D1@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B1 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B1; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; D2@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B2 (bulkhead); mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2700-02-02.stp (sha256 8510b8b0f1b648e7...) measured with wave2/straight/scripts/measure_bulkhead.py (prof.py section; validated: Brennan 2705-08-08 gives I1 1.44 = Air-Way): bulkhead tip 1.422 - relief start 0.352 (after the 0.04 collar) = 1.07; the -02 nose on the STEP = MS33656J JIC[2] (seat 0.1108, land 0.0662, relief 0.063); STEP overall 1.87 = catalog L 1.870, hex 0.5621 = catalog 0.562 [Brennan = yes 2026-10-18]; THDMAJ_B1@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); THDMAJ_B2@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); $PRP@Threads: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread texts, format of the built 2700 rows</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L4 / hex / bores from the Brennan TFA catalog p8, I1 measured on the Brennan 2700-02-02 STEP (no Air-Way -02 bulkhead)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2261,6 +2292,11 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>2700-02-02</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2418,24 +2454,50 @@
           <t>2700-LN-02-02</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.062</v>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>2700-LN-02-02</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5/16-24 x 5/16-24 (JIC) + bulkhead</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L4@DRIVE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "L LGTH" = "1.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - overall length [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; C2HEX@HEX: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - body hex [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 12/13 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2700-06-04 0.69 vs 0.812); D1@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B1 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B1 [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; D2@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B2 (bulkhead) [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2700-02-02.stp (sha256 8510b8b0f1b648e7...) measured with wave2/straight/scripts/measure_bulkhead.py (prof.py section; validated: Brennan 2705-08-08 gives I1 1.44 = Air-Way): bulkhead tip 1.422 - relief start 0.352 (after the 0.04 collar) = 1.07; the -02 nose on the STEP = MS33656J JIC[2] (seat 0.1108, land 0.0662, relief 0.063); STEP overall 1.87 = catalog L 1.870, hex 0.5621 = catalog 0.562 [Brennan = yes 2026-10-18] [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; THDMAJ_B1@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); THDMAJ_B2@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); $PRP@Threads: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread texts, format of the built 2700 rows</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L4 / hex / bores from the Brennan TFA catalog p8, I1 measured on the Brennan 2700-02-02 STEP (no Air-Way -02 bulkhead) - copied from the plain part (Q-TRANSFER-LN)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2446,6 +2508,11 @@
       <c r="O35" t="inlineStr">
         <is>
           <t>2700-LN-02-02</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
